--- a/output/graficos_dimensiones/comunal_d_env_a_2020_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:16</t>
+    <t xml:space="preserve">2026-09-10 01:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:30</t>
+    <t xml:space="preserve">2026-09-12 22:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:41</t>
+    <t xml:space="preserve">2026-09-24 00:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -505,7 +505,7 @@
         <v>2020</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>106.83</v>
+        <v>115.04</v>
       </c>
     </row>
     <row r="3">
@@ -522,7 +522,7 @@
         <v>2020</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>97.18</v>
+        <v>104.23</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +539,7 @@
         <v>2020</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>90.29</v>
+        <v>96.56</v>
       </c>
     </row>
     <row r="5">
@@ -556,7 +556,7 @@
         <v>2020</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>89.4</v>
+        <v>95.74</v>
       </c>
     </row>
     <row r="6">
@@ -573,7 +573,7 @@
         <v>2020</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>86.2</v>
+        <v>92.12</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
         <v>2020</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>82.64</v>
+        <v>88.31</v>
       </c>
     </row>
     <row r="8">
@@ -607,7 +607,7 @@
         <v>2020</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>71.89</v>
+        <v>76.87</v>
       </c>
     </row>
     <row r="9">
@@ -624,7 +624,7 @@
         <v>2020</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>64.39</v>
+        <v>69.61</v>
       </c>
     </row>
     <row r="10">
@@ -641,7 +641,7 @@
         <v>2020</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>53.14</v>
+        <v>56.78</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:10</t>
+    <t xml:space="preserve">2026-10-02 16:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:08</t>
+    <t xml:space="preserve">2026-10-05 16:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
